--- a/data/trans_camb/IP1002-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-1.403215655209112</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.6264628861597333</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.002049801589793</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.8156080323378445</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.215560692168348</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.720079330449342</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-3.733042656139868</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.150731353903357</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.230441758016991</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.937265004725397</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.674859075527698</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.403247340001886</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>0.2763522593239158</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.403311196874289</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.098565139130989</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.780528072664432</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.08282498391081455</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>1.47687360474501</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.5960252733553864</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.2660943181358077</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.3832108776917634</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.3119105152545953</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4898593974622819</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2901851213284428</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.9151188089178339</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.8309403582920714</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.8988929016735158</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7930184722942363</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8009444323781856</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.748298936678059</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2.578799977319877</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.9692040468619976</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.853962905096615</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.100489885898419</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.9194947279109515</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>0.01938531579868639</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.475464578549192</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.06648985127271773</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.8606099503570843</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.04464905178588677</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.6339074327220781</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-2.295607479071708</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.823544497963181</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.544079657554281</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.384302564521294</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-1.401175431799872</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.896612364005594</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>2.319006505621027</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.730346131789585</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.881812121970987</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.3371818810233206</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.462700097839584</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.6148723999554099</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.009796358732290107</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.2402757646218299</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.05573867146736774</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.7214522873234948</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.02816626817243402</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3998921820819719</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.7752544331923025</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.9464007387355234</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.6190982177321113</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8598557109442583</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +888,22 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>3.254966483828664</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2.708351603508095</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>6.68797550209678</v>
+      </c>
       <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>1.681792060108117</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.9378867956734398</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +916,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-2.212824057059949</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.523028993789638</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.975167187180249</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.8852163046062052</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-1.625631495598914</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.8961012804204372</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +942,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-5.321000331162376</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.467012797136786</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.470430847380555</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.404665594610454</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-3.315464071732825</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-2.926929108042939</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +968,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>0.4764833106505262</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.2417067825450916</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1757466378081227</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.512057271104059</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-0.2259399310592296</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.7440916740660722</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +994,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.6260375280370961</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.7137986544382526</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.7689284164611916</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.6980013071344895</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.6711145385663315</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.369940296399399</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1020,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.9314484832352684</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-1</v>
+      </c>
       <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="n">
+        <v>-0.9206099831016767</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.9234472476521863</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.8069581155405769</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1044,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.8125488221674407</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1.045776382168561</v>
+      </c>
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="n">
+        <v>0.1414058567381587</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.6773519787219655</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1070,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.8138468384344818</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.32420080613027</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.6754247425942016</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>1.300476682285705</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.1341125768918667</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.38626348590523</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1096,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-4.231619892979036</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.565426455806148</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.3442776840688713</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-1.919277273630382</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.330299655866622</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1122,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>1.98380909824948</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.01137822704487</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.414035093232888</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>3.716302285512776</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.508643451267189</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>2.2158171877991</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1148,28 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.3759653319866302</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1497680619384905</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.1128353593665976</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.3249820430894615</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1022,10 +1183,9 @@
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="n">
+        <v>-0.7507673199933316</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1039,10 +1199,9 @@
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="n">
+        <v>9.254291847201273</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1214,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.109434818935907</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-1.032680479464585</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.4540547891661199</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-0.2249324017114938</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.788831501724602</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.6365908035182921</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1240,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-2.48619715436287</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-2.339661557899788</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-1.510357470300342</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-1.347552865717696</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-1.507707429578818</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-1.538010787295601</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1266,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-0.06633528004111609</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.2074224364703231</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.4721322194027152</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.7509112292722475</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.008991892700473606</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.2231015163568327</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1292,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.4484679275176416</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.4174414454177697</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.2903186662868902</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.1438198129999166</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.3886129886434458</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.3136125448303209</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1318,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.7210192658311952</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.7344955238952889</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.7063001345031706</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.6542401728113734</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.6252780992516919</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.6297421346665304</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1344,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.02690980819485902</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.2035582517548259</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.5524598520644824</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.7163617365085554</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.01311533722959557</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.1877858282791726</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1372,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
